--- a/sharedata/excel/D-单位稀有度表(UnitRateData).xlsx
+++ b/sharedata/excel/D-单位稀有度表(UnitRateData).xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\策划文档\配置表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ThroneOfAshes_Client\sharedata\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="60">
   <si>
     <t>仅英雄生效</t>
   </si>
@@ -40,13 +40,13 @@
     <t>稀有度表</t>
   </si>
   <si>
-    <t>品质编号</t>
+    <t>稀有度编号</t>
   </si>
   <si>
     <t>检索名</t>
   </si>
   <si>
-    <t>品质名称</t>
+    <t>稀有度名称</t>
   </si>
   <si>
     <t>图标</t>
@@ -118,6 +118,9 @@
     <t>$Lang$稀有度.R</t>
   </si>
   <si>
+    <t>稀有度图标_R</t>
+  </si>
+  <si>
     <t>1星</t>
   </si>
   <si>
@@ -133,6 +136,9 @@
     <t>$Lang$稀有度.SR</t>
   </si>
   <si>
+    <t>稀有度图标_SR</t>
+  </si>
+  <si>
     <t>2星</t>
   </si>
   <si>
@@ -145,6 +151,9 @@
     <t>$Lang$稀有度.SSR</t>
   </si>
   <si>
+    <t>稀有度图标_SSR</t>
+  </si>
+  <si>
     <t>3星</t>
   </si>
   <si>
@@ -160,6 +169,9 @@
     <t>$Lang$稀有度.SSSR</t>
   </si>
   <si>
+    <t>稀有度图标_SSSR</t>
+  </si>
+  <si>
     <t>4星</t>
   </si>
   <si>
@@ -172,6 +184,9 @@
     <t>$Lang$稀有度.UR</t>
   </si>
   <si>
+    <t>稀有度图标_UR</t>
+  </si>
+  <si>
     <t>15星</t>
   </si>
   <si>
@@ -182,6 +197,9 @@
   </si>
   <si>
     <t>$Lang$稀有度.SP</t>
+  </si>
+  <si>
+    <t>稀有度图标_SP</t>
   </si>
   <si>
     <t>神话</t>
@@ -221,6 +239,9 @@
   <si>
     <t>$Lang$稀有度.UTR</t>
   </si>
+  <si>
+    <t>稀有度图标_UTR</t>
+  </si>
 </sst>
 </file>
 
@@ -232,7 +253,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <name val="微软雅黑"/>
@@ -261,6 +282,13 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="6" tint="0.4"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -289,13 +317,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFE58FBC"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -464,13 +485,6 @@
       <color rgb="FF78B4E8"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-      <b/>
-      <color rgb="FFFF0000"/>
     </font>
   </fonts>
   <fills count="34">
@@ -945,7 +959,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -976,6 +990,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -987,12 +1004,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1483,10 +1494,11 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="12.1111111111111" style="3" customWidth="1"/>
-    <col min="2" max="2" width="14" style="3" customWidth="1"/>
-    <col min="3" max="3" width="8.55555555555556" style="3" customWidth="1"/>
-    <col min="4" max="4" width="16.7777777777778" style="3" customWidth="1"/>
-    <col min="5" max="7" width="15.3333333333333" style="3" customWidth="1"/>
+    <col min="2" max="2" width="9.55555555555556" style="3" customWidth="1"/>
+    <col min="3" max="3" width="6.66666666666667" style="3" customWidth="1"/>
+    <col min="4" max="4" width="17.3333333333333" style="3" customWidth="1"/>
+    <col min="5" max="5" width="13.7777777777778" style="3" customWidth="1"/>
+    <col min="6" max="7" width="15.3333333333333" style="3" customWidth="1"/>
     <col min="8" max="16383" width="9" style="3" customWidth="1"/>
     <col min="16384" max="16384" width="9" style="3"/>
   </cols>
@@ -1510,18 +1522,14 @@
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>稀有度编号</t>
-        </is>
+      <c r="B3" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>稀有度名称</t>
-        </is>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>5</v>
@@ -1615,152 +1623,152 @@
       <c r="D7" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E7" t="str" s="14">
-        <v>稀有度图标_R</v>
+      <c r="E7" s="8" t="s">
+        <v>28</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="33.0" customHeight="1">
+    <row r="8" spans="1:7">
       <c r="A8" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>31</v>
+      <c r="C8" s="9" t="s">
+        <v>32</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" t="str" s="15">
-        <v>稀有度图标_SR</v>
+        <v>33</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="33.0" customHeight="1">
+    <row r="9" spans="1:7">
       <c r="A9" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B9">
         <v>3</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>35</v>
+      <c r="C9" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" t="str" s="15">
-        <v>稀有度图标_SSR</v>
+        <v>38</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>39</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="33.0" customHeight="1">
+    <row r="10" spans="1:7">
       <c r="A10" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B10">
         <v>4</v>
       </c>
-      <c r="C10" s="10" t="s">
-        <v>40</v>
+      <c r="C10" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="D10" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E10" t="str" s="15">
-        <v>稀有度图标_SSSR</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>38</v>
-      </c>
     </row>
-    <row r="11" spans="1:7" ht="33.0" customHeight="1">
+    <row r="11" spans="1:7">
       <c r="A11" s="3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B11">
         <v>5</v>
       </c>
-      <c r="C11" s="11" t="s">
-        <v>44</v>
+      <c r="C11" s="13" t="s">
+        <v>48</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" t="str" s="15">
-        <v>稀有度图标_UR</v>
+        <v>49</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>50</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="33.0" customHeight="1">
+    <row r="12" spans="1:7">
       <c r="A12" s="3" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B12">
         <v>6</v>
       </c>
-      <c r="C12" s="12" t="s">
-        <v>48</v>
+      <c r="C12" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="E12" t="str" s="15">
-        <v>稀有度图标_SP</v>
-      </c>
-      <c r="F12" t="str" s="14">
-        <v>5星</v>
-      </c>
-      <c r="G12" t="str" s="14">
-        <v>15星</v>
+        <v>54</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="33.0" customHeight="1">
+    <row r="13" spans="1:7">
       <c r="A13" s="3" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B13">
         <v>7</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" s="8" t="s">
         <v>51</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="E13" t="str" s="15">
-        <v>稀有度图标_UTR</v>
-      </c>
-      <c r="F13" t="str" s="14">
-        <v>5星</v>
-      </c>
-      <c r="G13" t="str" s="14">
-        <v>15星</v>
       </c>
     </row>
   </sheetData>
